--- a/tabtools/demo/demo_comptab.xlsx
+++ b/tabtools/demo/demo_comptab.xlsx
@@ -199,13 +199,13 @@
     <t>1.05 (0.98, 1.13)</t>
   </si>
   <si>
-    <t>"aHR = adjusted hazard ratio; CI = confidence interval. Models adjusted for age, sex, and comorbidities."</t>
+    <t>aHR = adjusted hazard ratio; CI = confidence interval. Models adjusted for age, sex, and comorbidities.</t>
   </si>
   <si>
     <t>Table S2. Selected Risk Factors (Name-Based Selection)</t>
   </si>
   <si>
-    <t>"Rows selected by label pattern using rownames() option."</t>
+    <t>Rows selected by label pattern using rownames() option.</t>
   </si>
 </sst>
 </file>

--- a/tabtools/demo/demo_comptab.xlsx
+++ b/tabtools/demo/demo_comptab.xlsx
@@ -212,7 +212,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1012">
+  <fonts count="976">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -645,38 +645,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
     </font>
     <font>
@@ -1601,38 +1569,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
     </font>
     <font>
@@ -2499,38 +2435,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
     </font>
     <font>
@@ -3368,30 +3272,6 @@
       <sz val="11"/>
       <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -4053,30 +3933,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
     </font>
     <font>
@@ -4409,997 +4265,12 @@
       <i/>
     </font>
   </fonts>
-  <fills count="209">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -5452,7 +4323,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="747">
+  <borders count="711">
     <border>
       <left/>
       <right/>
@@ -5958,62 +4829,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -7112,62 +5927,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -8273,62 +7032,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -9301,48 +8004,6 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
       <top style="medium"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -10054,48 +8715,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -10518,7 +9137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="747">
+  <cellXfs count="711">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -10742,110 +9361,110 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="106" fillId="2" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="107" fillId="3" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="4" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="5" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="6" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="7" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="8" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="9" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="115" fillId="10" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="117" fillId="11" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="119" fillId="12" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="13" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="122" fillId="14" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="15" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="16" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="17" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="18" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="19" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="20" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="21" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="22" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="23" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="24" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="25" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="26" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="27" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="137" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10855,7 +9474,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="139" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="140" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10867,65 +9486,65 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="142" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="28" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="29" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="30" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="31" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="32" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="33" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="34" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="35" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="36" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="37" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="38" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="154" fillId="39" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="40" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="41" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="155" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10942,11 +9561,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="42" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="43" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10974,11 +9593,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="44" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="45" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11006,36 +9625,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="177" fillId="46" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="178" fillId="47" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="177" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="180" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="181" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="182" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="183" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="184" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11078,674 +9697,674 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0"/>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="197" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="199" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="407" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="409" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="411" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="154" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="155" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="156" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" xfId="0"/>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="333" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="335" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="337" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="48" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="339" fillId="49" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="50" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="341" fillId="51" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="52" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="343" fillId="53" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="54" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="345" fillId="55" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="347" fillId="56" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="349" fillId="57" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="351" fillId="58" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="353" fillId="59" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="60" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="355" fillId="61" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="356" fillId="62" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="357" fillId="63" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="358" fillId="64" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="65" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="66" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="67" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="363" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="365" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="68" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="367" fillId="69" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="70" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="71" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="371" fillId="72" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="73" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="373" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="375" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="377" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="382" fillId="74" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="75" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="76" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="77" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="78" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="79" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="80" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="81" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="82" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="83" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="84" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="85" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="86" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="87" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="88" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="89" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="411" fillId="90" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="412" fillId="91" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="413" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="414" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="416" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="417" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="420" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="422" fillId="92" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="423" fillId="93" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="426" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="427" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="428" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="429" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="430" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="431" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="432" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="433" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11761,7 +10380,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="436" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="437" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11792,1631 +10411,1487 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" xfId="0"/>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="450" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="577" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="579" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="581" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="583" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="585" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="597" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="601" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="452" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="456" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="617" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="344" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="346" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="347" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="348" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" xfId="0"/>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="473" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="475" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="477" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="479" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="481" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="483" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="485" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="487" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="489" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="491" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="493" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="497" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="501" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="503" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="505" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="507" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="509" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="511" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="513" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="515" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="519" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="521" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="525" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="527" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="529" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="531" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="533" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="464" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="466" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="467" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="468" xfId="0"/>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="555" fillId="94" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="556" fillId="95" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="557" fillId="96" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="558" fillId="97" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="559" fillId="98" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="560" fillId="99" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="561" fillId="100" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="562" fillId="101" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="564" fillId="102" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="566" fillId="103" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="104" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="105" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="571" fillId="106" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="572" fillId="107" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="573" fillId="108" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="574" fillId="109" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="575" fillId="110" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="576" fillId="111" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="577" fillId="112" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="578" fillId="113" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="801" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="803" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="805" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="807" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="817" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="593" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="594" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="595" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="596" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="597" xfId="0"/>
+    <xf numFmtId="0" fontId="821" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="835" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="837" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="839" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="583" fillId="114" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="584" fillId="115" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="586" fillId="116" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="587" fillId="117" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="588" fillId="118" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="119" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="591" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="120" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="121" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="597" fillId="122" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="123" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="124" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="600" fillId="125" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="601" fillId="126" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="602" fillId="127" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="603" fillId="128" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="604" fillId="129" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="605" fillId="130" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="606" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="131" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="132" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="133" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="134" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="135" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="136" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="2" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="3" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="4" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="5" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="6" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="7" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="636" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="961" fillId="8" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="638" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="962" fillId="9" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="642" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="965" fillId="10" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="643" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="966" fillId="11" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="644" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="645" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="646" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="647" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="648" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="649" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="488" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="489" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="490" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="491" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="492" xfId="0"/>
-    <xf numFmtId="0" fontId="651" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="653" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="655" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="657" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="659" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="661" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="663" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="665" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="741" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="743" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="745" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="747" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="749" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="753" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="755" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="757" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="759" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="761" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="763" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="767" fillId="137" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="768" fillId="138" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="769" fillId="139" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="770" fillId="140" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="771" fillId="141" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="772" fillId="142" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="143" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="144" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="145" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="779" fillId="146" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="147" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="148" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="149" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="150" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="784" fillId="151" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="786" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="788" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="152" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="153" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="154" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="155" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="794" fillId="156" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="795" fillId="157" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="796" fillId="158" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="797" fillId="159" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="160" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="799" fillId="161" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="162" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="801" fillId="163" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="803" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="811" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="813" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="815" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="817" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="819" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="820" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="821" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="822" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="823" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="824" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="825" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="826" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="827" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="828" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="829" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="830" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="831" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="832" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="833" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="834" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="835" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="836" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="837" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="838" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="839" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="840" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="841" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="842" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="843" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="844" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="845" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="847" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="849" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="623" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="624" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="625" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="626" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="627" xfId="0"/>
-    <xf numFmtId="0" fontId="851" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="853" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="855" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="857" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="859" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="861" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="863" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="865" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="867" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="869" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="871" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="873" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="875" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="877" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="879" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="881" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="883" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="885" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="887" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="889" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="891" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="893" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="895" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="897" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="899" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="901" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="903" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="905" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="907" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="909" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="911" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="913" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="915" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="917" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="919" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="921" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="922" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="923" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="924" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="926" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="927" fillId="164" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="928" fillId="165" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="929" fillId="166" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="930" fillId="167" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="931" fillId="168" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="932" fillId="169" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="934" fillId="170" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="936" fillId="171" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="938" fillId="172" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="939" fillId="173" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="940" fillId="174" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="941" fillId="175" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="942" fillId="176" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="943" fillId="177" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="944" fillId="178" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="945" fillId="179" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="946" fillId="180" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="948" fillId="181" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="949" fillId="182" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="183" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="184" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="185" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="186" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="187" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="960" fillId="188" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="189" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="190" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="963" fillId="191" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="964" fillId="192" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="965" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="968" fillId="193" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="969" fillId="194" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="975" fillId="195" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="976" fillId="196" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="981" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="982" fillId="197" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="983" fillId="198" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="199" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="990" fillId="200" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="991" fillId="201" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="992" fillId="202" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="993" fillId="203" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="994" fillId="204" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="995" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="996" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="997" fillId="205" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="998" fillId="206" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="999" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1000" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1001" fillId="207" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1002" fillId="208" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1003" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1004" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1005" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1006" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1007" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1009" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1011" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13460,16 +11935,16 @@
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="103" t="s">
         <v>1</v>
       </c>
     </row>
@@ -13477,16 +11952,16 @@
       <c r="A3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="128" t="s">
+      <c r="B3" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="104" t="s">
+      <c r="C3" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="D3" s="97" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="112" t="s">
+      <c r="E3" s="104" t="s">
         <v>23</v>
       </c>
     </row>
@@ -13494,16 +11969,16 @@
       <c r="A4" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="135" t="s">
+      <c r="C4" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="136" t="s">
+      <c r="D4" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="137" t="s">
+      <c r="E4" s="129" t="s">
         <v>24</v>
       </c>
     </row>
@@ -13511,16 +11986,16 @@
       <c r="A5" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="122" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="138" t="s">
+      <c r="C5" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="139" t="s">
+      <c r="D5" s="131" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="140" t="s">
+      <c r="E5" s="132" t="s">
         <v>25</v>
       </c>
     </row>
@@ -13528,16 +12003,16 @@
       <c r="A6" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="141" t="s">
+      <c r="C6" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="142" t="s">
+      <c r="D6" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="143" t="s">
+      <c r="E6" s="135" t="s">
         <v>26</v>
       </c>
     </row>
@@ -13545,16 +12020,16 @@
       <c r="A7" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="132" t="s">
+      <c r="B7" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="144" t="s">
+      <c r="C7" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="145" t="s">
+      <c r="D7" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="146" t="s">
+      <c r="E7" s="138" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13562,16 +12037,16 @@
       <c r="A8" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="133" t="s">
+      <c r="B8" s="125" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="147" t="s">
+      <c r="C8" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="148" t="s">
+      <c r="D8" s="140" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="149" t="s">
+      <c r="E8" s="141" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13579,16 +12054,16 @@
       <c r="A9" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="150" t="s">
+      <c r="C9" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="151" t="s">
+      <c r="D9" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="152" t="s">
+      <c r="E9" s="144" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13605,214 +12080,214 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="154" customWidth="true"/>
-    <col min="2" max="2" width="28.7109375" style="155" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="156" customWidth="true"/>
-    <col min="4" max="4" width="12.2109375" style="157" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="158" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="146" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="147" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="148" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="149" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="150" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="153" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="227" t="s">
+    <row r="1" s="145" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="219" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="219" t="s">
+      <c r="B1" s="211" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="219" t="s">
+      <c r="C1" s="211" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="219" t="s">
+      <c r="D1" s="211" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="219" t="s">
+      <c r="E1" s="211" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="306" t="s">
+      <c r="B2" s="290" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="270" t="s">
+      <c r="C2" s="254" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="271" t="s">
+      <c r="D2" s="255" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="284" t="s">
+      <c r="E2" s="268" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="169" t="s">
+      <c r="A3" s="161" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="307" t="s">
+      <c r="B3" s="291" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="277" t="s">
+      <c r="C3" s="261" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="278" t="s">
+      <c r="D3" s="262" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="285" t="s">
+      <c r="E3" s="269" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="174" t="s">
+      <c r="A4" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="308" t="s">
+      <c r="B4" s="292" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="317" t="s">
+      <c r="C4" s="301" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="318" t="s">
+      <c r="D4" s="302" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="319" t="s">
+      <c r="E4" s="303" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="309" t="s">
+      <c r="B5" s="293" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="320" t="s">
+      <c r="C5" s="304" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="321" t="s">
+      <c r="D5" s="305" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="322" t="s">
+      <c r="E5" s="306" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="310" t="s">
+      <c r="B6" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="323" t="s">
+      <c r="C6" s="307" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="324" t="s">
+      <c r="D6" s="308" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="325" t="s">
+      <c r="E6" s="309" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="189" t="s">
+      <c r="A7" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="311" t="s">
+      <c r="B7" s="295" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="326" t="s">
+      <c r="C7" s="310" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="327" t="s">
+      <c r="D7" s="311" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="328" t="s">
+      <c r="E7" s="312" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="194" t="s">
+      <c r="A8" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="312" t="s">
+      <c r="B8" s="296" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="329" t="s">
+      <c r="C8" s="313" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="330" t="s">
+      <c r="D8" s="314" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="331" t="s">
+      <c r="E8" s="315" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="199" t="s">
+      <c r="A9" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="313" t="s">
+      <c r="B9" s="297" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="332" t="s">
+      <c r="C9" s="316" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="333" t="s">
+      <c r="D9" s="317" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="334" t="s">
+      <c r="E9" s="318" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="204" t="s">
+      <c r="A10" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="314" t="s">
+      <c r="B10" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="335" t="s">
+      <c r="C10" s="319" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="336" t="s">
+      <c r="D10" s="320" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="337" t="s">
+      <c r="E10" s="321" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="209" t="s">
+      <c r="A11" s="201" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="315" t="s">
+      <c r="B11" s="299" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="338" t="s">
+      <c r="C11" s="322" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="339" t="s">
+      <c r="D11" s="323" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="340" t="s">
+      <c r="E11" s="324" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="214" t="s">
+      <c r="A12" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="316" t="s">
+      <c r="B12" s="300" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="341" t="s">
+      <c r="C12" s="325" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="342" t="s">
+      <c r="D12" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="343" t="s">
+      <c r="E12" s="327" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13830,146 +12305,146 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="345" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="346" customWidth="true"/>
-    <col min="3" max="3" width="10.7109375" style="347" customWidth="true"/>
-    <col min="4" max="4" width="16.7109375" style="348" customWidth="true"/>
-    <col min="5" max="5" width="8.7109375" style="349" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="329" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="330" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" style="331" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="332" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="333" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="344" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="398" t="s">
+    <row r="1" s="328" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="382" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="390" t="s">
+      <c r="B1" s="374" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="390" t="s">
+      <c r="C1" s="374" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="390" t="s">
+      <c r="D1" s="374" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="390" t="s">
+      <c r="E1" s="374" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="355" t="s">
+      <c r="A2" s="339" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="462" t="s">
+      <c r="B2" s="438" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="434" t="s">
+      <c r="C2" s="410" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="435" t="s">
+      <c r="D2" s="411" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="448" t="s">
+      <c r="E2" s="424" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="360" t="s">
+      <c r="A3" s="344" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="463" t="s">
+      <c r="B3" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="441" t="s">
+      <c r="C3" s="417" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="442" t="s">
+      <c r="D3" s="418" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="449" t="s">
+      <c r="E3" s="425" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="365" t="s">
+      <c r="A4" s="349" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="464" t="s">
+      <c r="B4" s="440" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="473" t="s">
+      <c r="C4" s="449" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="474" t="s">
+      <c r="D4" s="450" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="475" t="s">
+      <c r="E4" s="451" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="370" t="s">
+      <c r="A5" s="354" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="469" t="s">
+      <c r="B5" s="445" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="476" t="s">
+      <c r="C5" s="452" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="477" t="s">
+      <c r="D5" s="453" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="478" t="s">
+      <c r="E5" s="454" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="375" t="s">
+      <c r="A6" s="359" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="466" t="s">
+      <c r="B6" s="442" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="479" t="s">
+      <c r="C6" s="455" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="480" t="s">
+      <c r="D6" s="456" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="481" t="s">
+      <c r="E6" s="457" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="380" t="s">
+      <c r="A7" s="364" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="467" t="s">
+      <c r="B7" s="443" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="482" t="s">
+      <c r="C7" s="458" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="483" t="s">
+      <c r="D7" s="459" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="484" t="s">
+      <c r="E7" s="460" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="385" t="s">
+      <c r="A8" s="369" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="468" t="s">
+      <c r="B8" s="444" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="485" t="s">
+      <c r="C8" s="461" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="486" t="s">
+      <c r="D8" s="462" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="487" t="s">
+      <c r="E8" s="463" t="s">
         <v>24</v>
       </c>
     </row>
@@ -13987,200 +12462,200 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="489" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="490" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="491" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="492" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="465" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="466" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="467" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="468" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="488" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="552" t="s">
+    <row r="1" s="464" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="528" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="545" t="s">
+      <c r="B1" s="521" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="545" t="s">
+      <c r="C1" s="521" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="545" t="s">
+      <c r="D1" s="521" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="497" t="s">
+      <c r="A2" s="473" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="575" t="s">
+      <c r="B2" s="545" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="576" t="s">
+      <c r="C2" s="546" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="577" t="s">
+      <c r="D2" s="547" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="501" t="s">
+      <c r="A3" s="477" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="580" t="s">
+      <c r="B3" s="550" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="581" t="s">
+      <c r="C3" s="551" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="582" t="s">
+      <c r="D3" s="552" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="505" t="s">
+      <c r="A4" s="481" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="589" t="s">
+      <c r="B4" s="559" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="598" t="s">
+      <c r="C4" s="568" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="599" t="s">
+      <c r="D4" s="569" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="509" t="s">
+      <c r="A5" s="485" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="510" t="s">
+      <c r="B5" s="486" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="600" t="s">
+      <c r="C5" s="570" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="601" t="s">
+      <c r="D5" s="571" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="513" t="s">
+      <c r="A6" s="489" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="514" t="s">
+      <c r="B6" s="490" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="602" t="s">
+      <c r="C6" s="572" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="603" t="s">
+      <c r="D6" s="573" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="517" t="s">
+      <c r="A7" s="493" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="518" t="s">
+      <c r="B7" s="494" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="604" t="s">
+      <c r="C7" s="574" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="605" t="s">
+      <c r="D7" s="575" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="521" t="s">
+      <c r="A8" s="497" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="522" t="s">
+      <c r="B8" s="498" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="606" t="s">
+      <c r="C8" s="576" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="607" t="s">
+      <c r="D8" s="577" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="525" t="s">
+      <c r="A9" s="501" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="595" t="s">
+      <c r="B9" s="565" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="608" t="s">
+      <c r="C9" s="578" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="609" t="s">
+      <c r="D9" s="579" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="529" t="s">
+      <c r="A10" s="505" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="530" t="s">
+      <c r="B10" s="506" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="610" t="s">
+      <c r="C10" s="580" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="611" t="s">
+      <c r="D10" s="581" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="533" t="s">
+      <c r="A11" s="509" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="534" t="s">
+      <c r="B11" s="510" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="612" t="s">
+      <c r="C11" s="582" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="613" t="s">
+      <c r="D11" s="583" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="537" t="s">
+      <c r="A12" s="513" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="538" t="s">
+      <c r="B12" s="514" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="614" t="s">
+      <c r="C12" s="584" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="615" t="s">
+      <c r="D12" s="585" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="541" t="s">
+      <c r="A13" s="517" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="583" t="s">
+      <c r="B13" s="553" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="616" t="s">
+      <c r="C13" s="586" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="617" t="s">
+      <c r="D13" s="587" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="622" t="s">
+      <c r="B14" s="592" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="490"/>
-      <c r="D14" s="490"/>
+      <c r="C14" s="466"/>
+      <c r="D14" s="466"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -14197,130 +12672,130 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="624" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="625" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="626" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="627" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="594" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="595" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="596" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="597" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="623" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="667" t="s">
+    <row r="1" s="593" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="637" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="660" t="s">
+      <c r="B1" s="630" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="660" t="s">
+      <c r="C1" s="630" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="660" t="s">
+      <c r="D1" s="630" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="632" t="s">
+      <c r="A2" s="602" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="719" t="s">
+      <c r="B2" s="683" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="695" t="s">
+      <c r="C2" s="659" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="705" t="s">
+      <c r="D2" s="669" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="636" t="s">
+      <c r="A3" s="606" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="720" t="s">
+      <c r="B3" s="684" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="700" t="s">
+      <c r="C3" s="664" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="706" t="s">
+      <c r="D3" s="670" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="640" t="s">
+      <c r="A4" s="610" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="721" t="s">
+      <c r="B4" s="685" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="732" t="s">
+      <c r="C4" s="696" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="733" t="s">
+      <c r="D4" s="697" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="644" t="s">
+      <c r="A5" s="614" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="726" t="s">
+      <c r="B5" s="690" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="734" t="s">
+      <c r="C5" s="698" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="735" t="s">
+      <c r="D5" s="699" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="648" t="s">
+      <c r="A6" s="618" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="723" t="s">
+      <c r="B6" s="687" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="736" t="s">
+      <c r="C6" s="700" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="737" t="s">
+      <c r="D6" s="701" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="652" t="s">
+      <c r="A7" s="622" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="729" t="s">
+      <c r="B7" s="693" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="738" t="s">
+      <c r="C7" s="702" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="739" t="s">
+      <c r="D7" s="703" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="656" t="s">
+      <c r="A8" s="626" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="725" t="s">
+      <c r="B8" s="689" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="740" t="s">
+      <c r="C8" s="704" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="741" t="s">
+      <c r="D8" s="705" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="746" t="s">
+      <c r="B9" s="710" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="625"/>
-      <c r="D9" s="625"/>
+      <c r="C9" s="595"/>
+      <c r="D9" s="595"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/tabtools/demo/demo_comptab.xlsx
+++ b/tabtools/demo/demo_comptab.xlsx
@@ -212,7 +212,55 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="976">
+  <fonts count="1046">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1026,6 +1074,78 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -2052,6 +2172,46 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -2803,6 +2963,86 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3616,6 +3856,46 @@
       <sz val="7"/>
       <name val="Arial"/>
       <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4323,7 +4603,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="711">
+  <borders count="781">
     <border>
       <left/>
       <right/>
@@ -4829,6 +5109,90 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -5927,6 +6291,132 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -7032,6 +7522,76 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -8004,6 +8564,146 @@
     <border>
       <left style="none"/>
       <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="medium"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -8715,6 +9415,76 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -9137,7 +9907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="711">
+  <cellXfs count="781">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -9145,384 +9915,384 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="152" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -9538,53 +10308,53 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="155" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="156" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="158" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="159" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="160" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="161" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="162" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="167" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9598,79 +10368,79 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="175" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="176" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="177" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="178" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="180" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="181" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="182" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="183" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="184" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="185" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="186" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="187" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="188" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="189" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -9697,570 +10467,570 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="145" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="146" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="147" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="148" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="149" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="150" xfId="0"/>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="206" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="325" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="162" xfId="0"/>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="270" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="327" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="329" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="331" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="333" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="335" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="337" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="339" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="340" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="341" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="343" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="345" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="346" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="347" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="349" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="351" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="353" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="355" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="357" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="358" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="360" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="362" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="363" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="364" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="365" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="366" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="367" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="398" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="371" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="373" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="403" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="375" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="405" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="377" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="378" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="382" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="407" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10268,15 +11038,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="408" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="409" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="410" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="411" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10296,7 +11066,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="415" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="416" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10304,601 +11074,601 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="417" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="423" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="420" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="422" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="423" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="426" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="428" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="429" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="431" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="432" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="434" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="435" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="440" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="441" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="442" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="443" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="328" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="331" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="333" xfId="0"/>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="451" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="473" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="475" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="477" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="479" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="481" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="483" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="485" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="487" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="489" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="491" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="493" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="497" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="501" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="503" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="505" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="507" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="509" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="511" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="513" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="515" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="519" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="521" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="525" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="527" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="529" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="531" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="533" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="534" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" xfId="0"/>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="529" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="531" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="533" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="535" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="537" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="539" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="541" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="543" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="545" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="547" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="549" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="551" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="553" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="555" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="557" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="559" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="561" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="563" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="565" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="567" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="569" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="571" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="573" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="575" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="536" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="538" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="540" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="542" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="544" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="546" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="587" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="548" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="589" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="550" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="591" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="552" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="593" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="554" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="595" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="556" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="558" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="599" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="560" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="562" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="603" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="564" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="605" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="566" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="568" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="570" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="572" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="607" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="609" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="611" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="613" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="615" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="577" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="579" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="581" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="583" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="585" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="587" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="591" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="597" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="600" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="601" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="602" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="604" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="606" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="617" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10906,992 +11676,1272 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="618" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="622" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="624" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="626" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="628" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="630" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="642" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="646" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="464" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="465" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="466" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="467" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="468" xfId="0"/>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="643" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="645" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="647" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="649" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="651" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="653" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="655" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="657" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="659" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="661" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="663" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="665" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="738" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="504" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="505" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="506" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="507" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="508" xfId="0"/>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="731" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="733" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="735" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="737" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="739" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="741" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="743" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="745" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="747" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="749" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="751" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="753" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="755" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="757" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="759" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="761" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="763" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="765" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="767" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="769" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="771" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="773" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="775" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="777" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="779" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="781" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="783" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="785" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="787" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="789" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="791" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="793" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="795" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="797" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="799" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="740" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="742" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="744" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="746" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="748" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="749" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="809" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="750" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="811" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="752" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="753" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="813" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="754" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="755" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="815" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="756" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="758" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="759" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="819" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="760" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="762" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="763" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="823" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="764" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="765" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="825" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="766" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="767" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="827" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="768" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="769" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="829" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="770" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="771" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="831" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="772" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="773" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="774" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="776" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="778" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="780" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="782" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="787" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="790" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="791" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="792" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="833" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="841" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="850" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="852" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="794" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="795" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="796" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="797" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="799" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="801" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="862" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="803" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="805" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="866" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="807" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="809" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="811" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="813" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="814" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="815" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="817" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="819" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="593" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="594" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="595" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="596" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="597" xfId="0"/>
-    <xf numFmtId="0" fontId="821" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="823" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="825" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="827" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="829" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="831" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="833" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="835" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="837" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="839" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="841" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="843" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="845" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="847" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="849" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="851" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="853" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="855" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="857" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="859" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="861" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="863" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="865" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="867" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="869" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="871" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="873" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="875" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="877" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="879" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="881" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="883" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="885" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="887" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="889" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="891" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="892" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="653" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="654" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="655" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="656" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="657" xfId="0"/>
+    <xf numFmtId="0" fontId="880" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="893" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="882" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="884" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="885" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="886" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="887" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="889" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="891" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="893" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="921" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="923" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="935" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="937" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="939" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="941" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="943" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="945" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="947" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="949" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="894" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="896" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="898" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="900" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="902" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="903" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="904" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="905" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="906" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="907" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="908" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="909" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="910" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="912" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="913" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="914" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="915" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="916" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="917" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="918" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="919" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="920" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="921" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="922" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="991" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="923" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="924" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="993" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="925" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="995" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="926" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="927" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="997" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="928" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="929" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="930" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="931" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="932" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="933" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="999" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1001" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1003" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="934" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="935" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="936" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="937" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="938" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="939" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="940" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1005" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1010" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="941" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="942" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="943" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="944" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="945" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="946" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="947" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1012" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1014" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1016" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="948" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="949" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="2" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="3" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="4" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="5" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="6" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="7" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1023" fillId="2" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1024" fillId="3" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1025" fillId="4" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1026" fillId="5" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1027" fillId="6" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1028" fillId="7" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="960" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="961" fillId="8" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1031" fillId="8" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="962" fillId="9" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1032" fillId="9" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="965" fillId="10" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1035" fillId="10" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="966" fillId="11" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1036" fillId="11" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="969" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11915,155 +12965,155 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="64" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="89" t="s">
+      <c r="C2" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="90" t="s">
+      <c r="D2" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="103" t="s">
+      <c r="E2" s="115" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="132" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="C3" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="104" t="s">
+      <c r="E3" s="116" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="127" t="s">
+      <c r="C4" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="128" t="s">
+      <c r="D4" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="129" t="s">
+      <c r="E4" s="141" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="122" t="s">
+      <c r="B5" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="130" t="s">
+      <c r="C5" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="131" t="s">
+      <c r="D5" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="132" t="s">
+      <c r="E5" s="144" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="123" t="s">
+      <c r="B6" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="133" t="s">
+      <c r="C6" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="134" t="s">
+      <c r="D6" s="146" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="135" t="s">
+      <c r="E6" s="147" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="124" t="s">
+      <c r="B7" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="136" t="s">
+      <c r="C7" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="137" t="s">
+      <c r="D7" s="149" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="138" t="s">
+      <c r="E7" s="150" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="139" t="s">
+      <c r="C8" s="151" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="140" t="s">
+      <c r="D8" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="141" t="s">
+      <c r="E8" s="153" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="126" t="s">
+      <c r="B9" s="138" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="142" t="s">
+      <c r="C9" s="154" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="143" t="s">
+      <c r="D9" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="144" t="s">
+      <c r="E9" s="156" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12080,214 +13130,214 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="146" customWidth="true"/>
-    <col min="2" max="2" width="28.7109375" style="147" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="148" customWidth="true"/>
-    <col min="4" max="4" width="12.2109375" style="149" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="150" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="158" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="159" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="160" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="161" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="162" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="145" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="219" t="s">
+    <row r="1" s="157" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="249" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="211" t="s">
+      <c r="B1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="211" t="s">
+      <c r="C1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="211" t="s">
+      <c r="D1" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="211" t="s">
+      <c r="E1" s="241" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="290" t="s">
+      <c r="B2" s="320" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="254" t="s">
+      <c r="C2" s="284" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="255" t="s">
+      <c r="D2" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="268" t="s">
+      <c r="E2" s="298" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="161" t="s">
+      <c r="A3" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="291" t="s">
+      <c r="B3" s="321" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="261" t="s">
+      <c r="C3" s="291" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="262" t="s">
+      <c r="D3" s="292" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="269" t="s">
+      <c r="E3" s="299" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="166" t="s">
+      <c r="A4" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="292" t="s">
+      <c r="B4" s="322" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="301" t="s">
+      <c r="C4" s="331" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="302" t="s">
+      <c r="D4" s="332" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="303" t="s">
+      <c r="E4" s="333" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="201" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="293" t="s">
+      <c r="B5" s="323" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="304" t="s">
+      <c r="C5" s="334" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="305" t="s">
+      <c r="D5" s="335" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="306" t="s">
+      <c r="E5" s="336" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="176" t="s">
+      <c r="A6" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="294" t="s">
+      <c r="B6" s="324" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="307" t="s">
+      <c r="C6" s="337" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="308" t="s">
+      <c r="D6" s="338" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="309" t="s">
+      <c r="E6" s="339" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="211" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="295" t="s">
+      <c r="B7" s="325" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="310" t="s">
+      <c r="C7" s="340" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="311" t="s">
+      <c r="D7" s="341" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="312" t="s">
+      <c r="E7" s="342" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="186" t="s">
+      <c r="A8" s="216" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="296" t="s">
+      <c r="B8" s="326" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="313" t="s">
+      <c r="C8" s="343" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="314" t="s">
+      <c r="D8" s="344" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="315" t="s">
+      <c r="E8" s="345" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="191" t="s">
+      <c r="A9" s="221" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="297" t="s">
+      <c r="B9" s="327" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="316" t="s">
+      <c r="C9" s="346" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="317" t="s">
+      <c r="D9" s="347" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="318" t="s">
+      <c r="E9" s="348" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="226" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="298" t="s">
+      <c r="B10" s="328" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="319" t="s">
+      <c r="C10" s="349" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="320" t="s">
+      <c r="D10" s="350" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="321" t="s">
+      <c r="E10" s="351" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="201" t="s">
+      <c r="A11" s="231" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="299" t="s">
+      <c r="B11" s="329" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="322" t="s">
+      <c r="C11" s="352" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="323" t="s">
+      <c r="D11" s="353" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="324" t="s">
+      <c r="E11" s="354" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="206" t="s">
+      <c r="A12" s="236" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="300" t="s">
+      <c r="B12" s="330" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="325" t="s">
+      <c r="C12" s="355" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="326" t="s">
+      <c r="D12" s="356" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="327" t="s">
+      <c r="E12" s="357" t="s">
         <v>27</v>
       </c>
     </row>
@@ -12305,146 +13355,146 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="329" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="330" customWidth="true"/>
-    <col min="3" max="3" width="10.7109375" style="331" customWidth="true"/>
-    <col min="4" max="4" width="16.7109375" style="332" customWidth="true"/>
-    <col min="5" max="5" width="8.7109375" style="333" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="359" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="360" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" style="361" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="362" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="363" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="328" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="382" t="s">
+    <row r="1" s="358" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="422" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="374" t="s">
+      <c r="B1" s="414" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="374" t="s">
+      <c r="C1" s="414" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="374" t="s">
+      <c r="D1" s="414" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="374" t="s">
+      <c r="E1" s="414" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="339" t="s">
+      <c r="A2" s="379" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="438" t="s">
+      <c r="B2" s="478" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="410" t="s">
+      <c r="C2" s="450" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="411" t="s">
+      <c r="D2" s="451" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="424" t="s">
+      <c r="E2" s="464" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="344" t="s">
+      <c r="A3" s="384" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="439" t="s">
+      <c r="B3" s="479" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="417" t="s">
+      <c r="C3" s="457" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="418" t="s">
+      <c r="D3" s="458" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="425" t="s">
+      <c r="E3" s="465" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="349" t="s">
+      <c r="A4" s="389" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="440" t="s">
+      <c r="B4" s="480" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="449" t="s">
+      <c r="C4" s="489" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="450" t="s">
+      <c r="D4" s="490" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="451" t="s">
+      <c r="E4" s="491" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="354" t="s">
+      <c r="A5" s="394" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="445" t="s">
+      <c r="B5" s="485" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="452" t="s">
+      <c r="C5" s="492" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="453" t="s">
+      <c r="D5" s="493" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="454" t="s">
+      <c r="E5" s="494" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="359" t="s">
+      <c r="A6" s="399" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="442" t="s">
+      <c r="B6" s="482" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="455" t="s">
+      <c r="C6" s="495" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="456" t="s">
+      <c r="D6" s="496" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="457" t="s">
+      <c r="E6" s="497" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="364" t="s">
+      <c r="A7" s="404" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="443" t="s">
+      <c r="B7" s="483" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="458" t="s">
+      <c r="C7" s="498" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="459" t="s">
+      <c r="D7" s="499" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="460" t="s">
+      <c r="E7" s="500" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="369" t="s">
+      <c r="A8" s="409" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="444" t="s">
+      <c r="B8" s="484" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="461" t="s">
+      <c r="C8" s="501" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="462" t="s">
+      <c r="D8" s="502" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="463" t="s">
+      <c r="E8" s="503" t="s">
         <v>24</v>
       </c>
     </row>
@@ -12462,196 +13512,196 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="465" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="466" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="467" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="468" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="505" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="506" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="507" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="508" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="464" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="528" t="s">
+    <row r="1" s="504" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="588" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="521" t="s">
+      <c r="B1" s="581" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="521" t="s">
+      <c r="C1" s="581" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="521" t="s">
+      <c r="D1" s="581" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="473" t="s">
+      <c r="A2" s="533" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="545" t="s">
+      <c r="B2" s="605" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="546" t="s">
+      <c r="C2" s="606" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="547" t="s">
+      <c r="D2" s="607" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="477" t="s">
+      <c r="A3" s="537" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="550" t="s">
+      <c r="B3" s="610" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="551" t="s">
+      <c r="C3" s="611" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="552" t="s">
+      <c r="D3" s="612" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="481" t="s">
+      <c r="A4" s="541" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="559" t="s">
+      <c r="B4" s="619" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="568" t="s">
+      <c r="C4" s="628" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="569" t="s">
+      <c r="D4" s="629" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="485" t="s">
+      <c r="A5" s="545" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="486" t="s">
+      <c r="B5" s="546" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="570" t="s">
+      <c r="C5" s="630" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="571" t="s">
+      <c r="D5" s="631" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="489" t="s">
+      <c r="A6" s="549" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="490" t="s">
+      <c r="B6" s="550" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="572" t="s">
+      <c r="C6" s="632" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="573" t="s">
+      <c r="D6" s="633" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="493" t="s">
+      <c r="A7" s="553" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="494" t="s">
+      <c r="B7" s="554" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="574" t="s">
+      <c r="C7" s="634" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="575" t="s">
+      <c r="D7" s="635" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="497" t="s">
+      <c r="A8" s="557" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="498" t="s">
+      <c r="B8" s="558" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="576" t="s">
+      <c r="C8" s="636" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="577" t="s">
+      <c r="D8" s="637" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="501" t="s">
+      <c r="A9" s="561" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="565" t="s">
+      <c r="B9" s="625" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="578" t="s">
+      <c r="C9" s="638" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="579" t="s">
+      <c r="D9" s="639" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="505" t="s">
+      <c r="A10" s="565" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="506" t="s">
+      <c r="B10" s="566" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="580" t="s">
+      <c r="C10" s="640" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="581" t="s">
+      <c r="D10" s="641" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="509" t="s">
+      <c r="A11" s="569" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="510" t="s">
+      <c r="B11" s="570" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="582" t="s">
+      <c r="C11" s="642" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="583" t="s">
+      <c r="D11" s="643" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="513" t="s">
+      <c r="A12" s="573" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="514" t="s">
+      <c r="B12" s="574" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="584" t="s">
+      <c r="C12" s="644" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="585" t="s">
+      <c r="D12" s="645" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="517" t="s">
+      <c r="A13" s="577" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="553" t="s">
+      <c r="B13" s="613" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="586" t="s">
+      <c r="C13" s="646" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="587" t="s">
+      <c r="D13" s="647" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="592" t="s">
+      <c r="B14" s="652" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="0"/>
@@ -12672,126 +13722,126 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="594" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="595" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="596" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="597" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="654" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="655" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="656" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="657" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="593" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="637" t="s">
+    <row r="1" s="653" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="707" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="630" t="s">
+      <c r="B1" s="700" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="630" t="s">
+      <c r="C1" s="700" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="630" t="s">
+      <c r="D1" s="700" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="602" t="s">
+      <c r="A2" s="672" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="683" t="s">
+      <c r="B2" s="753" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="659" t="s">
+      <c r="C2" s="729" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="669" t="s">
+      <c r="D2" s="739" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="606" t="s">
+      <c r="A3" s="676" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="684" t="s">
+      <c r="B3" s="754" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="664" t="s">
+      <c r="C3" s="734" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="670" t="s">
+      <c r="D3" s="740" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="610" t="s">
+      <c r="A4" s="680" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="685" t="s">
+      <c r="B4" s="755" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="696" t="s">
+      <c r="C4" s="766" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="697" t="s">
+      <c r="D4" s="767" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="614" t="s">
+      <c r="A5" s="684" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="690" t="s">
+      <c r="B5" s="760" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="698" t="s">
+      <c r="C5" s="768" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="699" t="s">
+      <c r="D5" s="769" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="618" t="s">
+      <c r="A6" s="688" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="687" t="s">
+      <c r="B6" s="757" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="700" t="s">
+      <c r="C6" s="770" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="701" t="s">
+      <c r="D6" s="771" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="622" t="s">
+      <c r="A7" s="692" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="693" t="s">
+      <c r="B7" s="763" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="702" t="s">
+      <c r="C7" s="772" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="703" t="s">
+      <c r="D7" s="773" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="626" t="s">
+      <c r="A8" s="696" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="689" t="s">
+      <c r="B8" s="759" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="704" t="s">
+      <c r="C8" s="774" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="705" t="s">
+      <c r="D8" s="775" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="710" t="s">
+      <c r="B9" s="780" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="0"/>

--- a/tabtools/demo/demo_comptab.xlsx
+++ b/tabtools/demo/demo_comptab.xlsx
@@ -212,7 +212,79 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1046">
+  <fonts count="1091">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1068,6 +1140,114 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4603,7 +4783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="781">
+  <borders count="826">
     <border>
       <left/>
       <right/>
@@ -5193,6 +5373,132 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -6417,6 +6723,195 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="none"/>
@@ -9907,7 +10402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="781">
+  <cellXfs count="826">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -9944,15 +10439,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -9960,350 +10455,350 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="34" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="36" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="39" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="40" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="41" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="42" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="43" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="44" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="45" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="46" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="47" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="48" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="49" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="50" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="51" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="52" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="53" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="54" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="55" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="56" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="57" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="58" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="59" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="60" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="61" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="62" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="63" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="64" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="65" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="66" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="67" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="68" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="69" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="70" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="71" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="72" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="73" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="74" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="75" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="76" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="77" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="78" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="80" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="81" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="82" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="149" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="83" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="139" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="141" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="143" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="149" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="150" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="151" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="152" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="153" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="154" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10312,11 +10807,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="156" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="157" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="158" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10324,63 +10819,63 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="159" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="161" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="163" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="165" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="167" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="160" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="161" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="174" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10388,19 +10883,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="175" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="176" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="177" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="178" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -10408,801 +10903,801 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="180" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="181" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="183" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="184" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="186" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="188" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="176" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="177" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="178" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="179" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="180" xfId="0"/>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="228" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="230" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="232" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="234" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="244" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="246" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="248" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="250" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="252" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="254" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="256" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="258" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="260" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="262" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="264" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="266" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="268" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="305" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="307" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="309" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="357" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="359" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="361" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="363" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="365" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="367" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="369" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="371" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="373" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="375" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="377" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="379" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="381" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="383" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="385" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="387" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="389" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="391" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="393" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="395" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="397" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="399" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="401" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="406" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="413" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="190" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="414" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="415" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="417" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="419" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="421" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="422" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="425" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="197" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="198" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="199" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="200" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="201" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="202" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="203" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="204" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="206" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="158" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="159" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="160" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="161" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="162" xfId="0"/>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="208" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="210" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="212" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="213" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="214" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="215" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="216" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="217" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="218" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="219" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="220" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="222" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="224" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="226" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="228" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="230" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="232" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="234" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="236" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="238" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="240" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="242" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="244" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="246" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="248" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="250" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="252" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="254" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="256" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="258" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="260" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="262" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="264" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="266" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="268" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="270" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="272" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="274" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="276" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="278" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="280" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="282" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="284" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="286" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="288" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="290" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="292" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="294" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="296" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="298" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="300" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="302" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="304" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="306" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="308" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="310" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="312" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="314" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="316" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="318" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="320" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="322" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="324" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="326" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="328" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="330" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="332" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="336" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="338" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="340" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="342" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="344" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="346" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="348" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="350" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="352" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="354" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="355" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="356" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="357" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="359" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="361" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="363" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="365" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="367" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="368" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="369" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="370" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="371" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="372" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="373" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="374" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="430" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="375" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="432" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="434" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="436" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="438" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="376" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="377" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="379" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="380" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="381" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="383" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="384" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="385" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="386" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="387" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="388" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="389" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="390" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="391" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="392" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="393" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="394" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="395" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="396" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="397" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="398" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="399" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="400" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="401" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="402" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="403" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="404" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="405" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="406" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="407" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="408" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="409" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="410" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="411" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="412" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="413" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="414" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="415" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="416" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="417" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="418" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="419" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="420" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="421" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="422" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="423" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="424" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="425" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="426" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="427" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="428" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="429" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="430" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="431" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="432" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="433" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="434" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="435" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="436" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="437" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="438" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="439" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="440" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="441" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="442" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="443" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="444" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="445" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="446" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="447" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="448" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="449" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="450" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11210,1271 +11705,1286 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="451" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="486" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="489" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="491" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="493" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="495" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="497" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="499" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="507" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="508" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="509" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="510" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="511" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="512" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="513" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="514" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="515" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="516" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="517" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="518" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="403" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="404" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="405" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="406" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="407" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="408" xfId="0"/>
+    <xf numFmtId="0" fontId="519" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="520" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="521" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="522" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="523" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="524" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="525" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="526" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="527" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="528" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="530" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="532" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="534" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="536" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="538" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="540" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="542" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="544" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="546" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="548" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="550" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="552" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="554" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="556" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="558" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="560" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="562" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="564" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="566" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="568" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="570" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="572" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="574" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="576" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="578" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="580" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="582" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="584" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="586" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="588" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="590" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="592" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="594" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="596" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="598" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="600" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="602" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="604" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="606" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="608" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="610" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="612" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="614" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="616" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="618" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="619" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="620" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="621" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="623" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="625" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="627" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="629" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="631" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="632" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="452" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="633" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="453" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="634" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="454" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="635" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="455" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="636" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="637" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="638" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="639" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="640" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="456" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="641" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="643" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="644" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="457" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="645" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="647" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="648" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="649" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="650" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="651" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="652" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="653" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="654" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="655" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="656" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="657" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="658" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="659" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="660" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="661" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="662" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="663" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="664" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="665" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="666" fillId="0" borderId="504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="667" fillId="0" borderId="505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="668" fillId="0" borderId="506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="669" fillId="0" borderId="507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="670" fillId="0" borderId="508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="671" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="672" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="673" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="674" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="675" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="676" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="677" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="678" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="679" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="680" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="681" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="682" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="683" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="684" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="685" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="686" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="687" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="688" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="689" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="690" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="691" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="692" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="693" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="694" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="695" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="696" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="458" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="697" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="459" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="698" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="460" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="699" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="461" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="700" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="462" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="701" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="463" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="702" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="703" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="464" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="704" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="465" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="705" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="466" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="706" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="467" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="707" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="468" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="708" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="469" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="709" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="470" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="710" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="471" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="549" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="550" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="551" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="552" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="553" xfId="0"/>
+    <xf numFmtId="0" fontId="711" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="712" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="713" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="714" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="715" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="716" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="717" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="718" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="719" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="720" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="721" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="722" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="723" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="724" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="725" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="726" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="727" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="728" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="729" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="730" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="732" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="734" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="736" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="738" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="740" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="742" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="744" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="746" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="748" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="750" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="752" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="754" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="756" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="758" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="760" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="762" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="764" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="766" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="768" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="770" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="772" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="774" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="776" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="778" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="780" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="782" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="784" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="786" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="788" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="790" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="792" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="794" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="796" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="798" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="800" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="802" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="804" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="806" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="808" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="810" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="812" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="814" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="816" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="818" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="820" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="822" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="824" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="826" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="828" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="830" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="832" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="834" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="836" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="838" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="840" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="842" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="843" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="844" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="845" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="847" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="849" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="851" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="853" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="854" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="472" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="855" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="473" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="856" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="358" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="361" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" xfId="0"/>
-    <xf numFmtId="0" fontId="474" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="475" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="476" fillId="0" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="477" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="478" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="479" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="857" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="858" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="859" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="860" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="861" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="863" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="864" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="865" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="867" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="868" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="869" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="870" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="871" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="872" fillId="0" borderId="653" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="873" fillId="0" borderId="654" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="874" fillId="0" borderId="655" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="875" fillId="0" borderId="656" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="876" fillId="0" borderId="657" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="877" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="480" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="878" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="879" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="881" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="481" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="482" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="483" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="485" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="487" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="489" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="491" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="493" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="495" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="497" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="499" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="501" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="503" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="505" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="507" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="509" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="511" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="513" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="515" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="517" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="519" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="521" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="523" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="525" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="527" fillId="0" borderId="395" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="529" fillId="0" borderId="396" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="531" fillId="0" borderId="397" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="533" fillId="0" borderId="398" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="535" fillId="0" borderId="399" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="537" fillId="0" borderId="400" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="539" fillId="0" borderId="401" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="541" fillId="0" borderId="402" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="543" fillId="0" borderId="403" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="545" fillId="0" borderId="404" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="547" fillId="0" borderId="405" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="549" fillId="0" borderId="406" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="551" fillId="0" borderId="407" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="553" fillId="0" borderId="408" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="555" fillId="0" borderId="409" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="557" fillId="0" borderId="410" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="559" fillId="0" borderId="411" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="561" fillId="0" borderId="412" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="563" fillId="0" borderId="413" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="565" fillId="0" borderId="414" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="567" fillId="0" borderId="415" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="569" fillId="0" borderId="416" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="571" fillId="0" borderId="417" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="573" fillId="0" borderId="418" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="574" fillId="0" borderId="419" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="575" fillId="0" borderId="420" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="576" fillId="0" borderId="421" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="578" fillId="0" borderId="422" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="580" fillId="0" borderId="423" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="582" fillId="0" borderId="424" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="584" fillId="0" borderId="425" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="586" fillId="0" borderId="426" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="587" fillId="0" borderId="427" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="588" fillId="0" borderId="428" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="589" fillId="0" borderId="429" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="590" fillId="0" borderId="430" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="591" fillId="0" borderId="431" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="592" fillId="0" borderId="432" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="593" fillId="0" borderId="433" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="594" fillId="0" borderId="434" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="595" fillId="0" borderId="435" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="596" fillId="0" borderId="436" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="598" fillId="0" borderId="437" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="599" fillId="0" borderId="438" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="600" fillId="0" borderId="439" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="602" fillId="0" borderId="440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="603" fillId="0" borderId="441" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="604" fillId="0" borderId="442" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="605" fillId="0" borderId="443" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="606" fillId="0" borderId="444" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="607" fillId="0" borderId="445" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="608" fillId="0" borderId="446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="609" fillId="0" borderId="447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="610" fillId="0" borderId="448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="611" fillId="0" borderId="449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="612" fillId="0" borderId="450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="613" fillId="0" borderId="451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="614" fillId="0" borderId="452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="615" fillId="0" borderId="453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="616" fillId="0" borderId="454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="617" fillId="0" borderId="455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="618" fillId="0" borderId="456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="619" fillId="0" borderId="457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="620" fillId="0" borderId="458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="621" fillId="0" borderId="459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="622" fillId="0" borderId="460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="623" fillId="0" borderId="461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="624" fillId="0" borderId="462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="625" fillId="0" borderId="463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="626" fillId="0" borderId="464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="627" fillId="0" borderId="465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="628" fillId="0" borderId="466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="629" fillId="0" borderId="467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="630" fillId="0" borderId="468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="631" fillId="0" borderId="469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="632" fillId="0" borderId="470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="633" fillId="0" borderId="471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="634" fillId="0" borderId="472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="635" fillId="0" borderId="473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="636" fillId="0" borderId="474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="637" fillId="0" borderId="475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="638" fillId="0" borderId="476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="639" fillId="0" borderId="477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="640" fillId="0" borderId="478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="641" fillId="0" borderId="479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="642" fillId="0" borderId="480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="643" fillId="0" borderId="481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="644" fillId="0" borderId="482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="645" fillId="0" borderId="483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="646" fillId="0" borderId="484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="647" fillId="0" borderId="485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="648" fillId="0" borderId="486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="649" fillId="0" borderId="487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="650" fillId="0" borderId="488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="651" fillId="0" borderId="489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="652" fillId="0" borderId="490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="653" fillId="0" borderId="491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="654" fillId="0" borderId="492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="655" fillId="0" borderId="493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="656" fillId="0" borderId="494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="657" fillId="0" borderId="495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="658" fillId="0" borderId="496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="659" fillId="0" borderId="497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="660" fillId="0" borderId="498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="661" fillId="0" borderId="499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="662" fillId="0" borderId="500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="663" fillId="0" borderId="501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="664" fillId="0" borderId="502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="665" fillId="0" borderId="503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="504" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="505" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="506" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="507" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="508" xfId="0"/>
-    <xf numFmtId="0" fontId="666" fillId="0" borderId="509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="667" fillId="0" borderId="510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="668" fillId="0" borderId="511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="669" fillId="0" borderId="512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="670" fillId="0" borderId="513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="671" fillId="0" borderId="514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="672" fillId="0" borderId="515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="673" fillId="0" borderId="516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="674" fillId="0" borderId="517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="675" fillId="0" borderId="518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="676" fillId="0" borderId="519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="677" fillId="0" borderId="520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="678" fillId="0" borderId="521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="679" fillId="0" borderId="522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="680" fillId="0" borderId="523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="681" fillId="0" borderId="524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="682" fillId="0" borderId="525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="683" fillId="0" borderId="526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="684" fillId="0" borderId="527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="685" fillId="0" borderId="528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="687" fillId="0" borderId="529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="689" fillId="0" borderId="530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="691" fillId="0" borderId="531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="693" fillId="0" borderId="532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="695" fillId="0" borderId="533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="697" fillId="0" borderId="534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="699" fillId="0" borderId="535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="701" fillId="0" borderId="536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="703" fillId="0" borderId="537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="705" fillId="0" borderId="538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="707" fillId="0" borderId="539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="709" fillId="0" borderId="540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="711" fillId="0" borderId="541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="713" fillId="0" borderId="542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="715" fillId="0" borderId="543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="717" fillId="0" borderId="544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="719" fillId="0" borderId="545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="721" fillId="0" borderId="546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="723" fillId="0" borderId="547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="725" fillId="0" borderId="548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="727" fillId="0" borderId="549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="729" fillId="0" borderId="550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="731" fillId="0" borderId="551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="733" fillId="0" borderId="552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="735" fillId="0" borderId="553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="737" fillId="0" borderId="554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="739" fillId="0" borderId="555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="741" fillId="0" borderId="556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="743" fillId="0" borderId="557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="745" fillId="0" borderId="558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="747" fillId="0" borderId="559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="749" fillId="0" borderId="560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="751" fillId="0" borderId="561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="753" fillId="0" borderId="562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="755" fillId="0" borderId="563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="757" fillId="0" borderId="564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="759" fillId="0" borderId="565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="761" fillId="0" borderId="566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="763" fillId="0" borderId="567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="765" fillId="0" borderId="568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="767" fillId="0" borderId="569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="769" fillId="0" borderId="570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="771" fillId="0" borderId="571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="773" fillId="0" borderId="572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="775" fillId="0" borderId="573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="777" fillId="0" borderId="574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="779" fillId="0" borderId="575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="781" fillId="0" borderId="576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="783" fillId="0" borderId="577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="785" fillId="0" borderId="578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="787" fillId="0" borderId="579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="789" fillId="0" borderId="580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="791" fillId="0" borderId="581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="793" fillId="0" borderId="582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="795" fillId="0" borderId="583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="797" fillId="0" borderId="584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="798" fillId="0" borderId="585" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="799" fillId="0" borderId="586" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="800" fillId="0" borderId="587" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="802" fillId="0" borderId="588" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="804" fillId="0" borderId="589" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="806" fillId="0" borderId="590" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="808" fillId="0" borderId="591" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="809" fillId="0" borderId="592" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="810" fillId="0" borderId="593" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="811" fillId="0" borderId="594" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="812" fillId="0" borderId="595" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="813" fillId="0" borderId="596" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="814" fillId="0" borderId="597" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="815" fillId="0" borderId="598" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="816" fillId="0" borderId="599" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="818" fillId="0" borderId="600" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="819" fillId="0" borderId="601" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="820" fillId="0" borderId="602" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="822" fillId="0" borderId="603" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="823" fillId="0" borderId="604" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="824" fillId="0" borderId="605" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="825" fillId="0" borderId="606" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="826" fillId="0" borderId="607" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="827" fillId="0" borderId="608" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="828" fillId="0" borderId="609" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="829" fillId="0" borderId="610" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="830" fillId="0" borderId="611" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="831" fillId="0" borderId="612" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="832" fillId="0" borderId="613" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="833" fillId="0" borderId="614" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="834" fillId="0" borderId="615" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="836" fillId="0" borderId="616" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="838" fillId="0" borderId="617" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="840" fillId="0" borderId="618" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="841" fillId="0" borderId="619" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="842" fillId="0" borderId="620" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="843" fillId="0" borderId="621" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="845" fillId="0" borderId="622" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="847" fillId="0" borderId="623" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="849" fillId="0" borderId="624" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="850" fillId="0" borderId="625" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="851" fillId="0" borderId="626" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="852" fillId="0" borderId="627" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="853" fillId="0" borderId="628" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="854" fillId="0" borderId="629" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="855" fillId="0" borderId="630" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="856" fillId="0" borderId="631" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="857" fillId="0" borderId="632" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="858" fillId="0" borderId="633" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="859" fillId="0" borderId="634" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="860" fillId="0" borderId="635" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="861" fillId="0" borderId="636" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="862" fillId="0" borderId="637" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="863" fillId="0" borderId="638" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="864" fillId="0" borderId="639" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="865" fillId="0" borderId="640" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="866" fillId="0" borderId="641" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="867" fillId="0" borderId="642" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="868" fillId="0" borderId="643" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="869" fillId="0" borderId="644" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="870" fillId="0" borderId="645" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="871" fillId="0" borderId="646" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="872" fillId="0" borderId="647" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="873" fillId="0" borderId="648" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="874" fillId="0" borderId="649" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="875" fillId="0" borderId="650" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="877" fillId="0" borderId="651" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="879" fillId="0" borderId="652" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="653" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="654" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="655" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="656" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="657" xfId="0"/>
-    <xf numFmtId="0" fontId="880" fillId="0" borderId="658" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="881" fillId="0" borderId="659" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="882" fillId="0" borderId="660" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="883" fillId="0" borderId="661" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="884" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="883" fillId="0" borderId="662" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="885" fillId="0" borderId="663" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="886" fillId="0" borderId="664" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -12482,466 +12992,631 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="887" fillId="0" borderId="665" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="888" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="890" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="888" fillId="0" borderId="666" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="892" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="894" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="895" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="889" fillId="0" borderId="667" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="896" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="897" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="898" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="899" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="900" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="901" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="902" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="903" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="904" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="905" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="906" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="907" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="908" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="909" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="910" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="911" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="912" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="913" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="914" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="915" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="916" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="917" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="918" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="919" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="920" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="922" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="924" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="698" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="699" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="700" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="701" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="702" xfId="0"/>
+    <xf numFmtId="0" fontId="925" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="926" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="927" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="928" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="929" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="930" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="891" fillId="0" borderId="668" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="893" fillId="0" borderId="669" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="895" fillId="0" borderId="670" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="897" fillId="0" borderId="671" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="899" fillId="0" borderId="672" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="901" fillId="0" borderId="673" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="903" fillId="0" borderId="674" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="905" fillId="0" borderId="675" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="907" fillId="0" borderId="676" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="909" fillId="0" borderId="677" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="911" fillId="0" borderId="678" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="913" fillId="0" borderId="679" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="915" fillId="0" borderId="680" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="917" fillId="0" borderId="681" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="931" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="919" fillId="0" borderId="682" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="921" fillId="0" borderId="683" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="923" fillId="0" borderId="684" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="925" fillId="0" borderId="685" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="932" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="927" fillId="0" borderId="686" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="929" fillId="0" borderId="687" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="931" fillId="0" borderId="688" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="933" fillId="0" borderId="689" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="933" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="935" fillId="0" borderId="690" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="937" fillId="0" borderId="691" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="939" fillId="0" borderId="692" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="941" fillId="0" borderId="693" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="934" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="943" fillId="0" borderId="694" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="945" fillId="0" borderId="695" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="947" fillId="0" borderId="696" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="949" fillId="0" borderId="697" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="936" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="938" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="940" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="942" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="944" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="946" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="948" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="698" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="699" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="700" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="0" borderId="701" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="702" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="0" borderId="703" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="0" borderId="704" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="990" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="992" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="994" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="996" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="998" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1000" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1002" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1004" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1006" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1007" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="705" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1008" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="706" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1009" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="707" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1011" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="708" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="709" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="710" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="711" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1013" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1015" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1017" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1018" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="712" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1019" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="713" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1020" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="976" fillId="0" borderId="714" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1021" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="715" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1022" fillId="0" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="716" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1023" fillId="0" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="717" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1024" fillId="0" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="718" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1025" fillId="0" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="982" fillId="0" borderId="719" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1027" fillId="0" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="983" fillId="0" borderId="720" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1028" fillId="0" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="721" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="722" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1029" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1030" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="723" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="724" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="725" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="0" borderId="726" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="990" fillId="0" borderId="727" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="991" fillId="0" borderId="728" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="992" fillId="0" borderId="729" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1031" fillId="0" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1032" fillId="0" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1033" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1034" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1035" fillId="0" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1036" fillId="0" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1037" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="993" fillId="0" borderId="730" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="994" fillId="0" borderId="731" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1038" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1039" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="995" fillId="0" borderId="732" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1040" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="996" fillId="0" borderId="733" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1041" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="997" fillId="0" borderId="734" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1042" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="998" fillId="0" borderId="735" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1043" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="999" fillId="0" borderId="736" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1044" fillId="0" borderId="781" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1000" fillId="0" borderId="737" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1001" fillId="0" borderId="738" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1002" fillId="0" borderId="739" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1003" fillId="0" borderId="740" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1045" fillId="0" borderId="782" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1046" fillId="0" borderId="783" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1047" fillId="0" borderId="784" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1048" fillId="0" borderId="785" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1004" fillId="0" borderId="741" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1005" fillId="0" borderId="742" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1006" fillId="0" borderId="743" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1007" fillId="0" borderId="744" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1008" fillId="0" borderId="745" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1009" fillId="0" borderId="746" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1010" fillId="0" borderId="747" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1049" fillId="0" borderId="786" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1050" fillId="0" borderId="787" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1051" fillId="0" borderId="788" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1052" fillId="0" borderId="789" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1053" fillId="0" borderId="790" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1054" fillId="0" borderId="791" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1055" fillId="0" borderId="792" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1011" fillId="0" borderId="748" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1056" fillId="0" borderId="793" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1012" fillId="0" borderId="749" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1057" fillId="0" borderId="794" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1013" fillId="0" borderId="750" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1058" fillId="0" borderId="795" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1014" fillId="0" borderId="751" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1059" fillId="0" borderId="796" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1015" fillId="0" borderId="752" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1060" fillId="0" borderId="797" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1016" fillId="0" borderId="753" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1017" fillId="0" borderId="754" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1061" fillId="0" borderId="798" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1062" fillId="0" borderId="799" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1018" fillId="0" borderId="755" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1063" fillId="0" borderId="800" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1019" fillId="0" borderId="756" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1064" fillId="0" borderId="801" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1020" fillId="0" borderId="757" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1065" fillId="0" borderId="802" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1021" fillId="0" borderId="758" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1066" fillId="0" borderId="803" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1022" fillId="0" borderId="759" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1067" fillId="0" borderId="804" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1023" fillId="2" borderId="760" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1068" fillId="2" borderId="805" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1024" fillId="3" borderId="761" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1025" fillId="4" borderId="762" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1026" fillId="5" borderId="763" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1069" fillId="3" borderId="806" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1070" fillId="4" borderId="807" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1071" fillId="5" borderId="808" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1027" fillId="6" borderId="764" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1028" fillId="7" borderId="765" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1029" fillId="0" borderId="766" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1072" fillId="6" borderId="809" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1073" fillId="7" borderId="810" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1074" fillId="0" borderId="811" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1030" fillId="0" borderId="767" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1075" fillId="0" borderId="812" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1031" fillId="8" borderId="768" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1076" fillId="8" borderId="813" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1032" fillId="9" borderId="769" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1077" fillId="9" borderId="814" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1033" fillId="0" borderId="770" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1078" fillId="0" borderId="815" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1034" fillId="0" borderId="771" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1079" fillId="0" borderId="816" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1035" fillId="10" borderId="772" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1080" fillId="10" borderId="817" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1036" fillId="11" borderId="773" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1081" fillId="11" borderId="818" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1037" fillId="0" borderId="774" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1082" fillId="0" borderId="819" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1038" fillId="0" borderId="775" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1083" fillId="0" borderId="820" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1039" fillId="0" borderId="776" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1084" fillId="0" borderId="821" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1040" fillId="0" borderId="777" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1085" fillId="0" borderId="822" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1041" fillId="0" borderId="778" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1086" fillId="0" borderId="823" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1043" fillId="0" borderId="779" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1088" fillId="0" borderId="824" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1045" fillId="0" borderId="780" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1090" fillId="0" borderId="825" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12965,155 +13640,155 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="82" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="102" t="s">
+      <c r="D2" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="115" t="s">
+      <c r="E2" s="133" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="C3" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="D3" s="127" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="116" t="s">
+      <c r="E3" s="134" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="133" t="s">
+      <c r="B4" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="139" t="s">
+      <c r="C4" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="140" t="s">
+      <c r="D4" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="141" t="s">
+      <c r="E4" s="159" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="142" t="s">
+      <c r="C5" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="143" t="s">
+      <c r="D5" s="161" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="144" t="s">
+      <c r="E5" s="162" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="135" t="s">
+      <c r="B6" s="153" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="145" t="s">
+      <c r="C6" s="163" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="146" t="s">
+      <c r="D6" s="164" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="147" t="s">
+      <c r="E6" s="165" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="136" t="s">
+      <c r="B7" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="148" t="s">
+      <c r="C7" s="166" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="149" t="s">
+      <c r="D7" s="167" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="150" t="s">
+      <c r="E7" s="168" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="151" t="s">
+      <c r="C8" s="169" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="152" t="s">
+      <c r="D8" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="153" t="s">
+      <c r="E8" s="171" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="59" t="s">
+      <c r="A9" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="138" t="s">
+      <c r="B9" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="154" t="s">
+      <c r="C9" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="155" t="s">
+      <c r="D9" s="173" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="156" t="s">
+      <c r="E9" s="174" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13130,214 +13805,214 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="158" customWidth="true"/>
-    <col min="2" max="2" width="28.7109375" style="159" customWidth="true"/>
-    <col min="3" max="3" width="7.7109375" style="160" customWidth="true"/>
-    <col min="4" max="4" width="12.2109375" style="161" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="162" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="176" customWidth="true"/>
+    <col min="2" max="2" width="28.7109375" style="177" customWidth="true"/>
+    <col min="3" max="3" width="7.7109375" style="178" customWidth="true"/>
+    <col min="4" max="4" width="12.2109375" style="179" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="180" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="157" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="249" t="s">
+    <row r="1" s="175" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="294" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="241" t="s">
+      <c r="B1" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="241" t="s">
+      <c r="C1" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="241" t="s">
+      <c r="D1" s="286" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="241" t="s">
+      <c r="E1" s="286" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="231" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="320" t="s">
+      <c r="B2" s="365" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="284" t="s">
+      <c r="C2" s="329" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="285" t="s">
+      <c r="D2" s="330" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="298" t="s">
+      <c r="E2" s="343" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="191" t="s">
+      <c r="A3" s="236" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="321" t="s">
+      <c r="B3" s="366" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="291" t="s">
+      <c r="C3" s="336" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="292" t="s">
+      <c r="D3" s="337" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="299" t="s">
+      <c r="E3" s="344" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="196" t="s">
+      <c r="A4" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="322" t="s">
+      <c r="B4" s="367" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="331" t="s">
+      <c r="C4" s="376" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="332" t="s">
+      <c r="D4" s="377" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="333" t="s">
+      <c r="E4" s="378" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="246" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="323" t="s">
+      <c r="B5" s="368" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="334" t="s">
+      <c r="C5" s="379" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="335" t="s">
+      <c r="D5" s="380" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="336" t="s">
+      <c r="E5" s="381" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="206" t="s">
+      <c r="A6" s="251" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="324" t="s">
+      <c r="B6" s="369" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="337" t="s">
+      <c r="C6" s="382" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="338" t="s">
+      <c r="D6" s="383" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="339" t="s">
+      <c r="E6" s="384" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="211" t="s">
+      <c r="A7" s="256" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="325" t="s">
+      <c r="B7" s="370" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="340" t="s">
+      <c r="C7" s="385" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="341" t="s">
+      <c r="D7" s="386" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="342" t="s">
+      <c r="E7" s="387" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="216" t="s">
+      <c r="A8" s="261" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="326" t="s">
+      <c r="B8" s="371" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="343" t="s">
+      <c r="C8" s="388" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="344" t="s">
+      <c r="D8" s="389" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="345" t="s">
+      <c r="E8" s="390" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="221" t="s">
+      <c r="A9" s="266" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="327" t="s">
+      <c r="B9" s="372" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="346" t="s">
+      <c r="C9" s="391" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="347" t="s">
+      <c r="D9" s="392" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="348" t="s">
+      <c r="E9" s="393" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="226" t="s">
+      <c r="A10" s="271" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="328" t="s">
+      <c r="B10" s="373" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="349" t="s">
+      <c r="C10" s="394" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="350" t="s">
+      <c r="D10" s="395" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="351" t="s">
+      <c r="E10" s="396" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="231" t="s">
+      <c r="A11" s="276" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="329" t="s">
+      <c r="B11" s="374" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="352" t="s">
+      <c r="C11" s="397" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="353" t="s">
+      <c r="D11" s="398" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="354" t="s">
+      <c r="E11" s="399" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="236" t="s">
+      <c r="A12" s="281" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="330" t="s">
+      <c r="B12" s="375" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="355" t="s">
+      <c r="C12" s="400" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="356" t="s">
+      <c r="D12" s="401" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="357" t="s">
+      <c r="E12" s="402" t="s">
         <v>27</v>
       </c>
     </row>
@@ -13355,146 +14030,146 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="359" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="360" customWidth="true"/>
-    <col min="3" max="3" width="10.7109375" style="361" customWidth="true"/>
-    <col min="4" max="4" width="16.7109375" style="362" customWidth="true"/>
-    <col min="5" max="5" width="8.7109375" style="363" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="404" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="405" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" style="406" customWidth="true"/>
+    <col min="4" max="4" width="16.7109375" style="407" customWidth="true"/>
+    <col min="5" max="5" width="8.7109375" style="408" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="358" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="422" t="s">
+    <row r="1" s="403" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="467" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="414" t="s">
+      <c r="B1" s="459" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="414" t="s">
+      <c r="C1" s="459" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="414" t="s">
+      <c r="D1" s="459" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="414" t="s">
+      <c r="E1" s="459" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="379" t="s">
+      <c r="A2" s="424" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="478" t="s">
+      <c r="B2" s="523" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="450" t="s">
+      <c r="C2" s="495" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="451" t="s">
+      <c r="D2" s="496" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="464" t="s">
+      <c r="E2" s="509" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="384" t="s">
+      <c r="A3" s="429" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="479" t="s">
+      <c r="B3" s="524" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="457" t="s">
+      <c r="C3" s="502" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="458" t="s">
+      <c r="D3" s="503" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="465" t="s">
+      <c r="E3" s="510" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="389" t="s">
+      <c r="A4" s="434" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="480" t="s">
+      <c r="B4" s="525" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="489" t="s">
+      <c r="C4" s="534" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="490" t="s">
+      <c r="D4" s="535" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="491" t="s">
+      <c r="E4" s="536" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="394" t="s">
+      <c r="A5" s="439" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="485" t="s">
+      <c r="B5" s="530" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="492" t="s">
+      <c r="C5" s="537" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="493" t="s">
+      <c r="D5" s="538" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="494" t="s">
+      <c r="E5" s="539" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="399" t="s">
+      <c r="A6" s="444" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="482" t="s">
+      <c r="B6" s="527" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="495" t="s">
+      <c r="C6" s="540" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="496" t="s">
+      <c r="D6" s="541" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="497" t="s">
+      <c r="E6" s="542" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="404" t="s">
+      <c r="A7" s="449" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="483" t="s">
+      <c r="B7" s="528" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="498" t="s">
+      <c r="C7" s="543" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="499" t="s">
+      <c r="D7" s="544" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="500" t="s">
+      <c r="E7" s="545" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="409" t="s">
+      <c r="A8" s="454" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="484" t="s">
+      <c r="B8" s="529" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="501" t="s">
+      <c r="C8" s="546" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="502" t="s">
+      <c r="D8" s="547" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="503" t="s">
+      <c r="E8" s="548" t="s">
         <v>24</v>
       </c>
     </row>
@@ -13512,196 +14187,196 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="505" customWidth="true"/>
-    <col min="2" max="2" width="18.7109375" style="506" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="507" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="508" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="550" customWidth="true"/>
+    <col min="2" max="2" width="18.7109375" style="551" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="552" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="553" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="504" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="588" t="s">
+    <row r="1" s="549" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="633" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="581" t="s">
+      <c r="B1" s="626" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="581" t="s">
+      <c r="C1" s="626" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="581" t="s">
+      <c r="D1" s="626" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="533" t="s">
+      <c r="A2" s="578" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="605" t="s">
+      <c r="B2" s="650" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="606" t="s">
+      <c r="C2" s="651" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="607" t="s">
+      <c r="D2" s="652" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="537" t="s">
+      <c r="A3" s="582" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="610" t="s">
+      <c r="B3" s="655" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="611" t="s">
+      <c r="C3" s="656" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="612" t="s">
+      <c r="D3" s="657" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="541" t="s">
+      <c r="A4" s="586" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="619" t="s">
+      <c r="B4" s="664" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="628" t="s">
+      <c r="C4" s="673" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="629" t="s">
+      <c r="D4" s="674" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="545" t="s">
+      <c r="A5" s="590" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="546" t="s">
+      <c r="B5" s="591" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="630" t="s">
+      <c r="C5" s="675" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="631" t="s">
+      <c r="D5" s="676" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="549" t="s">
+      <c r="A6" s="594" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="550" t="s">
+      <c r="B6" s="595" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="632" t="s">
+      <c r="C6" s="677" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="633" t="s">
+      <c r="D6" s="678" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="553" t="s">
+      <c r="A7" s="598" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="554" t="s">
+      <c r="B7" s="599" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="634" t="s">
+      <c r="C7" s="679" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="635" t="s">
+      <c r="D7" s="680" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="557" t="s">
+      <c r="A8" s="602" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="558" t="s">
+      <c r="B8" s="603" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="636" t="s">
+      <c r="C8" s="681" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="637" t="s">
+      <c r="D8" s="682" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="561" t="s">
+      <c r="A9" s="606" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="625" t="s">
+      <c r="B9" s="670" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="638" t="s">
+      <c r="C9" s="683" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="639" t="s">
+      <c r="D9" s="684" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="565" t="s">
+      <c r="A10" s="610" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="566" t="s">
+      <c r="B10" s="611" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="640" t="s">
+      <c r="C10" s="685" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="641" t="s">
+      <c r="D10" s="686" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="569" t="s">
+      <c r="A11" s="614" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="570" t="s">
+      <c r="B11" s="615" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="642" t="s">
+      <c r="C11" s="687" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="643" t="s">
+      <c r="D11" s="688" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="573" t="s">
+      <c r="A12" s="618" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="574" t="s">
+      <c r="B12" s="619" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="644" t="s">
+      <c r="C12" s="689" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="645" t="s">
+      <c r="D12" s="690" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="577" t="s">
+      <c r="A13" s="622" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="613" t="s">
+      <c r="B13" s="658" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="646" t="s">
+      <c r="C13" s="691" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="647" t="s">
+      <c r="D13" s="692" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="652" t="s">
+      <c r="B14" s="697" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="0"/>
@@ -13722,126 +14397,126 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="654" customWidth="true"/>
-    <col min="2" max="2" width="17.7109375" style="655" customWidth="true"/>
-    <col min="3" max="3" width="17.7109375" style="656" customWidth="true"/>
-    <col min="4" max="4" width="8.7109375" style="657" customWidth="true"/>
+    <col min="1" max="1" width="1.7109375" style="699" customWidth="true"/>
+    <col min="2" max="2" width="17.7109375" style="700" customWidth="true"/>
+    <col min="3" max="3" width="17.7109375" style="701" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="702" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="653" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="707" t="s">
+    <row r="1" s="698" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="752" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="700" t="s">
+      <c r="B1" s="745" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="700" t="s">
+      <c r="C1" s="745" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="700" t="s">
+      <c r="D1" s="745" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="672" t="s">
+      <c r="A2" s="717" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="753" t="s">
+      <c r="B2" s="798" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="729" t="s">
+      <c r="C2" s="774" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="739" t="s">
+      <c r="D2" s="784" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="676" t="s">
+      <c r="A3" s="721" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="754" t="s">
+      <c r="B3" s="799" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="734" t="s">
+      <c r="C3" s="779" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="740" t="s">
+      <c r="D3" s="785" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="680" t="s">
+      <c r="A4" s="725" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="755" t="s">
+      <c r="B4" s="800" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="766" t="s">
+      <c r="C4" s="811" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="767" t="s">
+      <c r="D4" s="812" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="684" t="s">
+      <c r="A5" s="729" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="760" t="s">
+      <c r="B5" s="805" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="768" t="s">
+      <c r="C5" s="813" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="769" t="s">
+      <c r="D5" s="814" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="688" t="s">
+      <c r="A6" s="733" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="757" t="s">
+      <c r="B6" s="802" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="770" t="s">
+      <c r="C6" s="815" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="771" t="s">
+      <c r="D6" s="816" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="692" t="s">
+      <c r="A7" s="737" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="763" t="s">
+      <c r="B7" s="808" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="772" t="s">
+      <c r="C7" s="817" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="773" t="s">
+      <c r="D7" s="818" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="696" t="s">
+      <c r="A8" s="741" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="759" t="s">
+      <c r="B8" s="804" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="774" t="s">
+      <c r="C8" s="819" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="775" t="s">
+      <c r="D8" s="820" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="780" t="s">
+      <c r="B9" s="825" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="0"/>
